--- a/data/processed/harmonization/Physical__Porosity/harmonized.xlsx
+++ b/data/processed/harmonization/Physical__Porosity/harmonized.xlsx
@@ -9254,12 +9254,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>187946:0-20</t>
+          <t>0-20:187946</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>187947:20-40</t>
+          <t>20-40:187947</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>187948:40-60</t>
+          <t>40-60:187948</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -9410,12 +9410,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>187949:60-100</t>
+          <t>60-100:187949</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>187950:0-20</t>
+          <t>0-20:187950</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>188051:20-40</t>
+          <t>20-40:188051</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9566,12 +9566,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>187951:40-60</t>
+          <t>40-60:187951</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>187952:60-100</t>
+          <t>60-100:187952</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>187955:0-20</t>
+          <t>0-20:187955</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>187956:20-40</t>
+          <t>20-40:187956</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>187957:40-60</t>
+          <t>40-60:187957</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>188054:60-100</t>
+          <t>60-100:188054</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>187953:0-20</t>
+          <t>0-20:187953</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -9930,12 +9930,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>187954:20-40</t>
+          <t>20-40:187954</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>188052:40-60</t>
+          <t>40-60:188052</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>188053:60-100</t>
+          <t>60-100:188053</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -10398,12 +10398,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
